--- a/artfynd/A 50546-2024 artfynd.xlsx
+++ b/artfynd/A 50546-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104854523</v>
       </c>
       <c r="B2" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>366296.8707141857</v>
+        <v>366297</v>
       </c>
       <c r="R2" t="n">
-        <v>6546200.672916037</v>
+        <v>6546200</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,110 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67530457</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>privat väg, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>366265</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6545867</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-09-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sanna Ryberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sanna Ryberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
